--- a/branches/migration/2026.0.0-template-v0.13.1/StructureDefinition-mii-pr-meta-searchparameter.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.1/StructureDefinition-mii-pr-meta-searchparameter.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
